--- a/data/Heat map 4-2 Society Impact and Inclusion.xlsx
+++ b/data/Heat map 4-2 Society Impact and Inclusion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0E0595-9FDB-4B49-8F38-AD5C26359478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6EFACB-995F-42C5-8180-F2201EAED1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -141,9 +141,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -523,7 +525,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -545,15 +547,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -563,15 +556,111 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -596,128 +685,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1026,937 +1034,937 @@
   <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="17" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="14" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="22" max="26" width="5" style="8" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="28" max="32" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="12"/>
+      <c r="C1" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
     </row>
-    <row r="2" spans="1:32" s="12" customFormat="1" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="65" t="s">
+    <row r="2" spans="1:32" s="9" customFormat="1" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="53"/>
+      <c r="B2" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="56" t="s">
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="56" t="s">
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="56" t="s">
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="56" t="s">
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="AB2" s="57"/>
-      <c r="AC2" s="57"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="58"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="44"/>
     </row>
     <row r="3" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="25"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="60" t="s">
+      <c r="A3" s="54"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="61" t="s">
+      <c r="H3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="60" t="s">
+      <c r="I3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="60" t="s">
+      <c r="K3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="60" t="s">
+      <c r="L3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="60" t="s">
+      <c r="M3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="61" t="s">
+      <c r="N3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="60" t="s">
+      <c r="O3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="60" t="s">
+      <c r="Q3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="60" t="s">
+      <c r="R3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="60" t="s">
+      <c r="S3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="60" t="s">
+      <c r="T3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="V3" s="60" t="s">
+      <c r="U3" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="60" t="s">
+      <c r="W3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="X3" s="60" t="s">
+      <c r="X3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="60" t="s">
+      <c r="Y3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="60" t="s">
+      <c r="Z3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="60" t="s">
+      <c r="AA3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AC3" s="60" t="s">
+      <c r="AC3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="AD3" s="60" t="s">
+      <c r="AD3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AE3" s="60" t="s">
+      <c r="AE3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="61" t="s">
+      <c r="AF3" s="34" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="33">
-        <v>0</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="37" t="s">
+      <c r="C4" s="55">
+        <v>0</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="39">
-        <v>0</v>
-      </c>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="39">
-        <v>0</v>
-      </c>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="39">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="35"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="61">
+        <v>0</v>
+      </c>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="61">
+        <v>0</v>
+      </c>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="18"/>
+      <c r="AA4" s="61">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="18"/>
     </row>
     <row r="5" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
+      <c r="A5" s="48"/>
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="56">
         <v>3</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="38" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="40">
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="62">
         <v>0.28999999999999998</v>
       </c>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="40">
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="62">
         <v>0.14000000000000001</v>
       </c>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="40">
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="62">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="36"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="19"/>
     </row>
     <row r="6" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="48"/>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="56">
         <v>1</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="38" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="40">
-        <v>0</v>
-      </c>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="40">
-        <v>0</v>
-      </c>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="36"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="62">
+        <v>0</v>
+      </c>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="62">
+        <v>0</v>
+      </c>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="19"/>
     </row>
     <row r="7" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="15">
-        <v>0</v>
-      </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="38" t="s">
+      <c r="C7" s="56">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="40">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="62">
         <v>0.43</v>
       </c>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="40">
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="62">
         <v>0.28999999999999998</v>
       </c>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="40">
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="62">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="36"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="19"/>
     </row>
     <row r="8" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="47" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="56">
         <v>5</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="38" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="40">
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="62">
         <v>0.33</v>
       </c>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="40">
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="62">
         <v>0.33</v>
       </c>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="36"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="19"/>
     </row>
     <row r="9" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="56">
         <v>3</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="38" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="40">
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="62">
         <v>0.44</v>
       </c>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="40">
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="62">
         <v>0.44</v>
       </c>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="40">
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="62">
         <v>0.11</v>
       </c>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="30"/>
-      <c r="AD9" s="30"/>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="36"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="19"/>
     </row>
     <row r="10" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15">
-        <v>0</v>
-      </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="38" t="s">
+      <c r="C10" s="56">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="40">
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="62">
         <v>0.56999999999999995</v>
       </c>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="40">
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="62">
         <v>0.71</v>
       </c>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="36"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="19"/>
     </row>
     <row r="11" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="15">
-        <v>0</v>
-      </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="38" t="s">
+      <c r="C11" s="56">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="40">
-        <v>0</v>
-      </c>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="40">
-        <v>0</v>
-      </c>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="36"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="62">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="62">
+        <v>0</v>
+      </c>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="19"/>
     </row>
     <row r="12" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="50" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="15">
-        <v>0</v>
-      </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="38" t="s">
+      <c r="C12" s="56">
+        <v>0</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="40">
-        <v>0</v>
-      </c>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="40">
-        <v>0</v>
-      </c>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="36"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="62">
+        <v>0</v>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="62">
+        <v>0</v>
+      </c>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="19"/>
     </row>
     <row r="13" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="56">
         <v>3</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="38" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="40">
-        <v>0</v>
-      </c>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="40">
-        <v>0</v>
-      </c>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="36"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="62">
+        <v>0</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="62">
+        <v>0</v>
+      </c>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="19"/>
     </row>
     <row r="14" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="56">
         <v>3</v>
       </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="38" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="40">
-        <v>0</v>
-      </c>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="40">
-        <v>0</v>
-      </c>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="30"/>
-      <c r="AC14" s="30"/>
-      <c r="AD14" s="30"/>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="36"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="62">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="62">
+        <v>0</v>
+      </c>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="16"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="19"/>
     </row>
     <row r="15" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="38" t="s">
+      <c r="C15" s="56">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="40">
-        <v>0</v>
-      </c>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="40">
-        <v>0</v>
-      </c>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="30"/>
-      <c r="AD15" s="30"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="36"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="62">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="62">
+        <v>0</v>
+      </c>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="19"/>
     </row>
     <row r="16" spans="1:32" s="1" customFormat="1" ht="13.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="23"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="41">
-        <v>0</v>
-      </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="44" t="s">
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="45">
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="63">
         <v>1</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="45">
-        <v>0</v>
-      </c>
-      <c r="V16" s="42"/>
-      <c r="W16" s="42"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="42"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="45">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="42"/>
-      <c r="AC16" s="42"/>
-      <c r="AD16" s="42"/>
-      <c r="AE16" s="42"/>
-      <c r="AF16" s="43"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="63">
+        <v>0</v>
+      </c>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="63">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" s="47" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="58">
         <v>30</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="50">
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="65">
         <v>15</v>
       </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="51">
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="64">
         <v>0.25</v>
       </c>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="51">
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="64">
         <v>0.25</v>
       </c>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="51">
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="64">
         <v>0.25</v>
       </c>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="14"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="11"/>
     </row>
     <row r="18" spans="1:32" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
-      <c r="B18" s="48" t="s">
+      <c r="A18" s="39"/>
+      <c r="B18" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="59">
         <f>SUM(C4:C16)</f>
         <v>18</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="46">
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="66">
         <v>30</v>
       </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="46" t="s">
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="46" t="s">
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="V18" s="28"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="46" t="s">
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" s="28"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="29"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="14"/>
+      <c r="AF18" s="15"/>
     </row>
     <row r="19" spans="1:32" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="32"/>
-      <c r="B19" s="49" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="60">
         <v>2.3076923076923075</v>
       </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="53" t="s">
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="54">
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="67">
         <v>0.25</v>
       </c>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="52"/>
-      <c r="U19" s="54">
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="67">
         <v>0.25</v>
       </c>
-      <c r="V19" s="52"/>
-      <c r="W19" s="52"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="52"/>
-      <c r="Z19" s="52"/>
-      <c r="AA19" s="54">
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="67">
         <v>0.25</v>
       </c>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="52"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="52"/>
-      <c r="AF19" s="55"/>
+      <c r="AB19" s="29"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="31"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
+      <c r="A20" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="12">
